--- a/outputs/table/table1_baseline_characteristics_internal.xlsx
+++ b/outputs/table/table1_baseline_characteristics_internal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>Characteristic</t>
   </si>
@@ -67,76 +67,70 @@
     <t>— Canon</t>
   </si>
   <si>
-    <t>59.7 ± 12.4</t>
+    <t>59.7 ± 12.1</t>
   </si>
   <si>
     <t>20–89</t>
   </si>
   <si>
-    <t>169.7 ± 5.9</t>
-  </si>
-  <si>
-    <t>69.7 ± 10.0</t>
-  </si>
-  <si>
-    <t>24.2 ± 2.9</t>
-  </si>
-  <si>
-    <t>184 (47.2%)</t>
-  </si>
-  <si>
-    <t>105 (26.9%)</t>
-  </si>
-  <si>
-    <t>62 (15.9%)</t>
-  </si>
-  <si>
-    <t>210 (53.8%)</t>
-  </si>
-  <si>
-    <t>69 (17.7%)</t>
-  </si>
-  <si>
-    <t>111 (28.5%)</t>
-  </si>
-  <si>
-    <t>0 (0.0%)</t>
-  </si>
-  <si>
-    <t>55.5 ± 11.7</t>
-  </si>
-  <si>
-    <t>23–91</t>
-  </si>
-  <si>
-    <t>158.0 ± 6.0</t>
-  </si>
-  <si>
-    <t>57.6 ± 8.2</t>
-  </si>
-  <si>
-    <t>23.1 ± 3.1</t>
-  </si>
-  <si>
-    <t>145 (20.8%)</t>
-  </si>
-  <si>
-    <t>99 (14.2%)</t>
-  </si>
-  <si>
-    <t>21 (3.0%)</t>
-  </si>
-  <si>
-    <t>356 (51.0%)</t>
-  </si>
-  <si>
-    <t>249 (35.7%)</t>
-  </si>
-  <si>
-    <t>91 (13.0%)</t>
-  </si>
-  <si>
-    <t>2 (0.3%)</t>
+    <t>170.0 ± 5.8</t>
+  </si>
+  <si>
+    <t>69.5 ± 8.9</t>
+  </si>
+  <si>
+    <t>24.0 ± 2.6</t>
+  </si>
+  <si>
+    <t>216 (45.5%)</t>
+  </si>
+  <si>
+    <t>127 (26.7%)</t>
+  </si>
+  <si>
+    <t>73 (15.4%)</t>
+  </si>
+  <si>
+    <t>273 (57.5%)</t>
+  </si>
+  <si>
+    <t>2 (0.4%)</t>
+  </si>
+  <si>
+    <t>55.8 ± 12.0</t>
+  </si>
+  <si>
+    <t>22–91</t>
+  </si>
+  <si>
+    <t>158.5 ± 5.7</t>
+  </si>
+  <si>
+    <t>57.5 ± 7.9</t>
+  </si>
+  <si>
+    <t>22.9 ± 3.1</t>
+  </si>
+  <si>
+    <t>169 (21.6%)</t>
+  </si>
+  <si>
+    <t>105 (13.4%)</t>
+  </si>
+  <si>
+    <t>32 (4.1%)</t>
+  </si>
+  <si>
+    <t>415 (52.9%)</t>
+  </si>
+  <si>
+    <t>256 (32.7%)</t>
+  </si>
+  <si>
+    <t>109 (13.9%)</t>
+  </si>
+  <si>
+    <t>4 (0.5%)</t>
   </si>
   <si>
     <t>&lt;0.001</t>
@@ -522,10 +516,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -536,7 +530,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -547,10 +541,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -561,10 +555,10 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -575,10 +569,10 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -589,10 +583,10 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -603,10 +597,10 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -617,10 +611,10 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -628,7 +622,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -639,7 +633,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -647,10 +641,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -658,10 +652,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -669,10 +663,10 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
